--- a/etf_holdings/2026-09-02_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:12</t>
+          <t>2026-09-02 00:56:42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:12</t>
+          <t>2026-09-02 00:56:42</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:12</t>
+          <t>2026-09-02 00:56:42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:12</t>
+          <t>2026-09-02 00:56:42</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:12</t>
+          <t>2026-09-02 00:56:42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:12</t>
+          <t>2026-09-02 00:56:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:12</t>
+          <t>2026-09-02 00:56:42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:12</t>
+          <t>2026-09-02 00:56:42</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:12</t>
+          <t>2026-09-02 00:56:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:12</t>
+          <t>2026-09-02 00:56:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:12</t>
+          <t>2026-09-02 00:56:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:12</t>
+          <t>2026-09-02 00:56:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:12</t>
+          <t>2026-09-02 00:56:42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:12</t>
+          <t>2026-09-02 00:56:42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:12</t>
+          <t>2026-09-02 00:56:42</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:13</t>
+          <t>2026-09-02 00:56:43</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:13</t>
+          <t>2026-09-02 00:56:43</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:13</t>
+          <t>2026-09-02 00:56:43</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:13</t>
+          <t>2026-09-02 00:56:43</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:13</t>
+          <t>2026-09-02 00:56:43</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:13</t>
+          <t>2026-09-02 00:56:43</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:13</t>
+          <t>2026-09-02 00:56:43</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:13</t>
+          <t>2026-09-02 00:56:43</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:13</t>
+          <t>2026-09-02 00:56:43</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:13</t>
+          <t>2026-09-02 00:56:43</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:13</t>
+          <t>2026-09-02 00:56:43</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:13</t>
+          <t>2026-09-02 00:56:43</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:13</t>
+          <t>2026-09-02 00:56:43</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:13</t>
+          <t>2026-09-02 00:56:43</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:13</t>
+          <t>2026-09-02 00:56:43</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:15</t>
+          <t>2026-09-02 00:56:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:15</t>
+          <t>2026-09-02 00:56:45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:15</t>
+          <t>2026-09-02 00:56:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:15</t>
+          <t>2026-09-02 00:56:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:15</t>
+          <t>2026-09-02 00:56:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:15</t>
+          <t>2026-09-02 00:56:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:15</t>
+          <t>2026-09-02 00:56:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:15</t>
+          <t>2026-09-02 00:56:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:15</t>
+          <t>2026-09-02 00:56:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:15</t>
+          <t>2026-09-02 00:56:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:15</t>
+          <t>2026-09-02 00:56:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:15</t>
+          <t>2026-09-02 00:56:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:15</t>
+          <t>2026-09-02 00:56:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:15</t>
+          <t>2026-09-02 00:56:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:15</t>
+          <t>2026-09-02 00:56:45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:16</t>
+          <t>2026-09-02 00:56:46</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:16</t>
+          <t>2026-09-02 00:56:46</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:16</t>
+          <t>2026-09-02 00:56:46</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:16</t>
+          <t>2026-09-02 00:56:46</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:16</t>
+          <t>2026-09-02 00:56:46</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-02_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:42</t>
+          <t>2026-09-02 01:22:27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:42</t>
+          <t>2026-09-02 01:22:27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:42</t>
+          <t>2026-09-02 01:22:27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:42</t>
+          <t>2026-09-02 01:22:27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:42</t>
+          <t>2026-09-02 01:22:27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:42</t>
+          <t>2026-09-02 01:22:27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:42</t>
+          <t>2026-09-02 01:22:27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:42</t>
+          <t>2026-09-02 01:22:27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:42</t>
+          <t>2026-09-02 01:22:27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:42</t>
+          <t>2026-09-02 01:22:27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:42</t>
+          <t>2026-09-02 01:22:27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:42</t>
+          <t>2026-09-02 01:22:27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:42</t>
+          <t>2026-09-02 01:22:27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:42</t>
+          <t>2026-09-02 01:22:27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:42</t>
+          <t>2026-09-02 01:22:27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:43</t>
+          <t>2026-09-02 01:22:28</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:43</t>
+          <t>2026-09-02 01:22:28</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:43</t>
+          <t>2026-09-02 01:22:28</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:43</t>
+          <t>2026-09-02 01:22:28</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:43</t>
+          <t>2026-09-02 01:22:28</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:43</t>
+          <t>2026-09-02 01:22:28</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:43</t>
+          <t>2026-09-02 01:22:28</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:43</t>
+          <t>2026-09-02 01:22:28</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:43</t>
+          <t>2026-09-02 01:22:28</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:43</t>
+          <t>2026-09-02 01:22:28</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:43</t>
+          <t>2026-09-02 01:22:28</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:43</t>
+          <t>2026-09-02 01:22:28</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:43</t>
+          <t>2026-09-02 01:22:28</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:43</t>
+          <t>2026-09-02 01:22:28</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:43</t>
+          <t>2026-09-02 01:22:28</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:45</t>
+          <t>2026-09-02 01:22:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:45</t>
+          <t>2026-09-02 01:22:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:45</t>
+          <t>2026-09-02 01:22:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:45</t>
+          <t>2026-09-02 01:22:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:45</t>
+          <t>2026-09-02 01:22:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:45</t>
+          <t>2026-09-02 01:22:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:45</t>
+          <t>2026-09-02 01:22:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:45</t>
+          <t>2026-09-02 01:22:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:45</t>
+          <t>2026-09-02 01:22:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:45</t>
+          <t>2026-09-02 01:22:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:45</t>
+          <t>2026-09-02 01:22:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:45</t>
+          <t>2026-09-02 01:22:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:45</t>
+          <t>2026-09-02 01:22:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:45</t>
+          <t>2026-09-02 01:22:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:45</t>
+          <t>2026-09-02 01:22:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:46</t>
+          <t>2026-09-02 01:22:31</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:46</t>
+          <t>2026-09-02 01:22:31</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:46</t>
+          <t>2026-09-02 01:22:31</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:46</t>
+          <t>2026-09-02 01:22:31</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:46</t>
+          <t>2026-09-02 01:22:31</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-02_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:27</t>
+          <t>2026-09-02 16:26:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.46%2440</t>
+          <t>-2.25%2385</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>-2.25%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2440</v>
+        <v>2385</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:27</t>
+          <t>2026-09-02 16:26:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+9.94%7800</t>
+          <t>0%2610</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>7800</v>
+        <v>2610</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:27</t>
+          <t>2026-09-02 16:26:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.44%3410</t>
+          <t>-2.93%3310</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-2.93%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3410</v>
+        <v>3310</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:27</t>
+          <t>2026-09-02 16:26:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+2.83%5640</t>
+          <t>-3.46%5445</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5640</v>
+        <v>5445</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:27</t>
+          <t>2026-09-02 16:26:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+9.94%4315</t>
+          <t>-0.93%4275</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4315</v>
+        <v>4275</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.46%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:27</t>
+          <t>2026-09-02 16:26:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-2.8%971</t>
+          <t>+0.21%973</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:27</t>
+          <t>2026-09-02 16:26:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+1.36%1865</t>
+          <t>-7.24%1730</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-7.24%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1865</v>
+        <v>1730</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:27</t>
+          <t>2026-09-02 16:26:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.21%14150</t>
+          <t>-2.01%13865</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-2.01%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>14150</v>
+        <v>13865</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:27</t>
+          <t>2026-09-02 16:26:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-1.72%5995</t>
+          <t>-1.67%5895</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-1.72%</t>
+          <t>-1.67%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5995</v>
+        <v>5895</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:27</t>
+          <t>2026-09-02 16:26:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+1.05%1450</t>
+          <t>-2.76%1410</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>-2.76%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1450</v>
+        <v>1410</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:27</t>
+          <t>2026-09-02 16:26:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+8.35%2205</t>
+          <t>-2.95%2140</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+8.35%</t>
+          <t>-2.95%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2205</v>
+        <v>2140</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:27</t>
+          <t>2026-09-02 16:26:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.87%2285</t>
+          <t>-7.66%2110</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.87%</t>
+          <t>-7.66%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2285</v>
+        <v>2110</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:27</t>
+          <t>2026-09-02 16:26:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.41%1225</t>
+          <t>-2.04%1200</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1225</v>
+        <v>1200</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:27</t>
+          <t>2026-09-02 16:26:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+5.46%5410</t>
+          <t>-2.22%5290</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+5.46%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5410</v>
+        <v>5290</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:27</t>
+          <t>2026-09-02 16:26:26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+4.45%610</t>
+          <t>-3.44%589</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+4.45%</t>
+          <t>-3.44%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>610</v>
+        <v>589</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:28</t>
+          <t>2026-09-02 16:26:27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,16 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+5.15%1225</t>
+          <t>-4.08%1175</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+5.15%</t>
+          <t>-4.08%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1225</v>
+        <v>1175</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:28</t>
+          <t>2026-09-02 16:26:27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+4.22%568</t>
+          <t>-4.93%540</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+4.22%</t>
+          <t>-4.93%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>568</v>
+        <v>540</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:28</t>
+          <t>2026-09-02 16:26:27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+6.68%2315</t>
+          <t>-6.26%2170</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+6.68%</t>
+          <t>-6.26%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2315</v>
+        <v>2170</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:28</t>
+          <t>2026-09-02 16:26:27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,16 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+6.57%17120</t>
+          <t>+3.53%17725</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+6.57%</t>
+          <t>+3.53%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>17120</v>
+        <v>17725</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:28</t>
+          <t>2026-09-02 16:26:27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+5.02%711</t>
+          <t>-2.67%692</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+5.02%</t>
+          <t>-2.67%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>711</v>
+        <v>692</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:28</t>
+          <t>2026-09-02 16:26:27</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.75%5885</t>
+          <t>-1.95%5770</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5885</v>
+        <v>5770</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:28</t>
+          <t>2026-09-02 16:26:27</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+7%535</t>
+          <t>-5.23%507</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+7%</t>
+          <t>-5.23%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>535</v>
+        <v>507</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:28</t>
+          <t>2026-09-02 16:26:27</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+3.57%2030</t>
+          <t>-2.71%1975</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+3.57%</t>
+          <t>-2.71%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2030</v>
+        <v>1975</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:28</t>
+          <t>2026-09-02 16:26:27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-2.97%3425</t>
+          <t>-0.88%3395</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-2.97%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>3425</v>
+        <v>3395</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:28</t>
+          <t>2026-09-02 16:26:27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-0.92%7580</t>
+          <t>+3.03%7810</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+3.03%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>7580</v>
+        <v>7810</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:28</t>
+          <t>2026-09-02 16:26:27</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-4.6%518</t>
+          <t>0%518</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:28</t>
+          <t>2026-09-02 16:26:27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+10%2640</t>
+          <t>-9.28%2395</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>-9.28%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2640</v>
+        <v>2395</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:28</t>
+          <t>2026-09-02 16:26:27</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.48%300.5</t>
+          <t>+4.83%315</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.48%</t>
+          <t>+4.83%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>300.5</v>
+        <v>315</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:28</t>
+          <t>2026-09-02 16:26:27</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+2.23%1375</t>
+          <t>-2.55%1340</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+2.23%</t>
+          <t>-2.55%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1375</v>
+        <v>1340</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:28</t>
+          <t>2026-09-02 16:26:27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+2.71%132.5</t>
+          <t>-4.91%126</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+2.71%</t>
+          <t>-4.91%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>132.5</v>
+        <v>126</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:30</t>
+          <t>2026-09-02 16:26:28</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0%1175</t>
+          <t>+7.66%1265</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+7.66%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1175</v>
+        <v>1265</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:30</t>
+          <t>2026-09-02 16:26:28</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+2.17%990</t>
+          <t>-2.22%968</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>990</v>
+        <v>968</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:30</t>
+          <t>2026-09-02 16:26:28</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+2.22%552</t>
+          <t>-1.63%543</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+2.22%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:30</t>
+          <t>2026-09-02 16:26:28</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-3.3%234.5</t>
+          <t>+1.28%237.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>234.5</v>
+        <v>237.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:30</t>
+          <t>2026-09-02 16:26:28</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+0.44%114.5</t>
+          <t>-2.18%112</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>-2.18%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>114.5</v>
+        <v>112</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:30</t>
+          <t>2026-09-02 16:26:28</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-2.6%711</t>
+          <t>-0.42%708</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:30</t>
+          <t>2026-09-02 16:26:28</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+8.93%744</t>
+          <t>-5.38%704</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+8.93%</t>
+          <t>-5.38%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>744</v>
+        <v>704</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:30</t>
+          <t>2026-09-02 16:26:28</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+7.25%1480</t>
+          <t>-2.36%1445</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+7.25%</t>
+          <t>-2.36%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1480</v>
+        <v>1445</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:30</t>
+          <t>2026-09-02 16:26:28</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0%1450</t>
+          <t>-2.07%1420</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1450</v>
+        <v>1420</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:30</t>
+          <t>2026-09-02 16:26:28</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-6.09%1310</t>
+          <t>-0.38%1305</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-6.09%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1310</v>
+        <v>1305</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:30</t>
+          <t>2026-09-02 16:26:28</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+3.34%958</t>
+          <t>-0.1%957</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+3.34%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:30</t>
+          <t>2026-09-02 16:26:28</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+0.17%295</t>
+          <t>+0.51%296.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>295</v>
+        <v>296.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:30</t>
+          <t>2026-09-02 16:26:28</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.85%2125</t>
+          <t>-2.82%2065</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>-2.82%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2125</v>
+        <v>2065</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:30</t>
+          <t>2026-09-02 16:26:28</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.36%412</t>
+          <t>+0.12%412.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>412</v>
+        <v>412.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:30</t>
+          <t>2026-09-02 16:26:28</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+3.19%744</t>
+          <t>0%744</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+3.19%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:31</t>
+          <t>2026-09-02 16:26:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,17 +3254,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+4.85%540</t>
+          <t>-0.93%535</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+4.85%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>535</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:31</t>
+          <t>2026-09-02 16:26:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3317,17 +3317,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-3.56%176</t>
+          <t>+1.7%179</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-3.56%</t>
+          <t>+1.7%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>179</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:31</t>
+          <t>2026-09-02 16:26:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3380,17 +3380,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+1.4%1445</t>
+          <t>-3.46%1395</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+1.4%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:31</t>
+          <t>2026-09-02 16:26:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3443,17 +3443,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0%136</t>
+          <t>+1.1%137.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:31</t>
+          <t>2026-09-02 16:26:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3506,17 +3506,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+9.84%3125</t>
+          <t>+9.92%3435</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+9.84%</t>
+          <t>+9.92%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">

--- a/etf_holdings/2026-09-02_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:26</t>
+          <t>2026-09-02 19:49:42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:26</t>
+          <t>2026-09-02 19:49:42</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:26</t>
+          <t>2026-09-02 19:49:42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:26</t>
+          <t>2026-09-02 19:49:42</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:26</t>
+          <t>2026-09-02 19:49:42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:26</t>
+          <t>2026-09-02 19:49:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:26</t>
+          <t>2026-09-02 19:49:42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:26</t>
+          <t>2026-09-02 19:49:42</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:26</t>
+          <t>2026-09-02 19:49:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:26</t>
+          <t>2026-09-02 19:49:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:26</t>
+          <t>2026-09-02 19:49:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:26</t>
+          <t>2026-09-02 19:49:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:26</t>
+          <t>2026-09-02 19:49:42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:26</t>
+          <t>2026-09-02 19:49:42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:26</t>
+          <t>2026-09-02 19:49:42</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:27</t>
+          <t>2026-09-02 19:49:44</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:27</t>
+          <t>2026-09-02 19:49:44</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:27</t>
+          <t>2026-09-02 19:49:44</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:27</t>
+          <t>2026-09-02 19:49:44</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:27</t>
+          <t>2026-09-02 19:49:44</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:27</t>
+          <t>2026-09-02 19:49:44</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:27</t>
+          <t>2026-09-02 19:49:44</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:27</t>
+          <t>2026-09-02 19:49:44</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:27</t>
+          <t>2026-09-02 19:49:44</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:27</t>
+          <t>2026-09-02 19:49:44</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:27</t>
+          <t>2026-09-02 19:49:44</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:27</t>
+          <t>2026-09-02 19:49:44</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:27</t>
+          <t>2026-09-02 19:49:44</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:27</t>
+          <t>2026-09-02 19:49:44</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:27</t>
+          <t>2026-09-02 19:49:44</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:28</t>
+          <t>2026-09-02 19:49:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:28</t>
+          <t>2026-09-02 19:49:45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:28</t>
+          <t>2026-09-02 19:49:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:28</t>
+          <t>2026-09-02 19:49:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:28</t>
+          <t>2026-09-02 19:49:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:28</t>
+          <t>2026-09-02 19:49:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:28</t>
+          <t>2026-09-02 19:49:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:28</t>
+          <t>2026-09-02 19:49:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:28</t>
+          <t>2026-09-02 19:49:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:28</t>
+          <t>2026-09-02 19:49:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:28</t>
+          <t>2026-09-02 19:49:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:28</t>
+          <t>2026-09-02 19:49:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:28</t>
+          <t>2026-09-02 19:49:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:28</t>
+          <t>2026-09-02 19:49:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:28</t>
+          <t>2026-09-02 19:49:45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:30</t>
+          <t>2026-09-02 19:49:46</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:30</t>
+          <t>2026-09-02 19:49:46</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:30</t>
+          <t>2026-09-02 19:49:46</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:30</t>
+          <t>2026-09-02 19:49:46</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:30</t>
+          <t>2026-09-02 19:49:46</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-02_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:42</t>
+          <t>2026-09-02 22:21:44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:42</t>
+          <t>2026-09-02 22:21:44</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:42</t>
+          <t>2026-09-02 22:21:44</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:42</t>
+          <t>2026-09-02 22:21:44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:42</t>
+          <t>2026-09-02 22:21:44</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:42</t>
+          <t>2026-09-02 22:21:44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:42</t>
+          <t>2026-09-02 22:21:44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:42</t>
+          <t>2026-09-02 22:21:44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:42</t>
+          <t>2026-09-02 22:21:44</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:42</t>
+          <t>2026-09-02 22:21:44</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:42</t>
+          <t>2026-09-02 22:21:44</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:42</t>
+          <t>2026-09-02 22:21:44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:42</t>
+          <t>2026-09-02 22:21:44</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:42</t>
+          <t>2026-09-02 22:21:44</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:42</t>
+          <t>2026-09-02 22:21:44</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:44</t>
+          <t>2026-09-02 22:21:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:44</t>
+          <t>2026-09-02 22:21:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:44</t>
+          <t>2026-09-02 22:21:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:44</t>
+          <t>2026-09-02 22:21:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:44</t>
+          <t>2026-09-02 22:21:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:44</t>
+          <t>2026-09-02 22:21:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:44</t>
+          <t>2026-09-02 22:21:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:44</t>
+          <t>2026-09-02 22:21:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:44</t>
+          <t>2026-09-02 22:21:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:44</t>
+          <t>2026-09-02 22:21:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:44</t>
+          <t>2026-09-02 22:21:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:44</t>
+          <t>2026-09-02 22:21:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:44</t>
+          <t>2026-09-02 22:21:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:44</t>
+          <t>2026-09-02 22:21:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:44</t>
+          <t>2026-09-02 22:21:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:45</t>
+          <t>2026-09-02 22:21:47</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:45</t>
+          <t>2026-09-02 22:21:47</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:45</t>
+          <t>2026-09-02 22:21:47</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:45</t>
+          <t>2026-09-02 22:21:47</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:45</t>
+          <t>2026-09-02 22:21:47</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:45</t>
+          <t>2026-09-02 22:21:47</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:45</t>
+          <t>2026-09-02 22:21:47</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:45</t>
+          <t>2026-09-02 22:21:47</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:45</t>
+          <t>2026-09-02 22:21:47</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:45</t>
+          <t>2026-09-02 22:21:47</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:45</t>
+          <t>2026-09-02 22:21:47</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:45</t>
+          <t>2026-09-02 22:21:47</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:45</t>
+          <t>2026-09-02 22:21:47</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:45</t>
+          <t>2026-09-02 22:21:47</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:45</t>
+          <t>2026-09-02 22:21:47</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:46</t>
+          <t>2026-09-02 22:21:48</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:46</t>
+          <t>2026-09-02 22:21:48</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:46</t>
+          <t>2026-09-02 22:21:48</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:46</t>
+          <t>2026-09-02 22:21:48</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:46</t>
+          <t>2026-09-02 22:21:48</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
